--- a/outputs/ToT_(Labour/Cereal)_tukey_classification_matrix.xlsx
+++ b/outputs/ToT_(Labour/Cereal)_tukey_classification_matrix.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2550" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2550" uniqueCount="134">
   <si>
     <t>2020 May</t>
   </si>
@@ -347,6 +347,9 @@
   </si>
   <si>
     <t>Alarm</t>
+  </si>
+  <si>
+    <t>No data</t>
   </si>
   <si>
     <t>23%</t>
@@ -1240,13 +1243,13 @@
         <v>108</v>
       </c>
       <c r="BU2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BV2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BW2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="3" spans="1:75">
@@ -1467,13 +1470,13 @@
         <v>108</v>
       </c>
       <c r="BU3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="BV3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="BW3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="4" spans="1:75">
@@ -1694,13 +1697,13 @@
         <v>108</v>
       </c>
       <c r="BU4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="BV4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="BW4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="5" spans="1:75">
@@ -1921,13 +1924,13 @@
         <v>108</v>
       </c>
       <c r="BU5" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="BV5" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="BW5" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="6" spans="1:75">
@@ -2148,13 +2151,13 @@
         <v>108</v>
       </c>
       <c r="BU6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="BV6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BW6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="7" spans="1:75">
@@ -2327,61 +2330,61 @@
         <v>108</v>
       </c>
       <c r="BE7" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BF7" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BG7" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BH7" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BI7" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BJ7" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BK7" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BL7" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BM7" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BN7" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BO7" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BP7" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BQ7" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BR7" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BS7" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BT7" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BU7" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="BV7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="BW7" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="8" spans="1:75">
@@ -2602,13 +2605,13 @@
         <v>108</v>
       </c>
       <c r="BU8" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="BV8" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="BW8" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="9" spans="1:75">
@@ -2829,13 +2832,13 @@
         <v>108</v>
       </c>
       <c r="BU9" t="s">
+        <v>119</v>
+      </c>
+      <c r="BV9" t="s">
+        <v>115</v>
+      </c>
+      <c r="BW9" t="s">
         <v>118</v>
-      </c>
-      <c r="BV9" t="s">
-        <v>114</v>
-      </c>
-      <c r="BW9" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="10" spans="1:75">
@@ -3056,13 +3059,13 @@
         <v>108</v>
       </c>
       <c r="BU10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="BV10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="BW10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="11" spans="1:75">
@@ -3283,13 +3286,13 @@
         <v>108</v>
       </c>
       <c r="BU11" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="BV11" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="BW11" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="12" spans="1:75">
@@ -3510,13 +3513,13 @@
         <v>108</v>
       </c>
       <c r="BU12" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="BV12" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="BW12" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="13" spans="1:75">
@@ -3737,13 +3740,13 @@
         <v>108</v>
       </c>
       <c r="BU13" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="BV13" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BW13" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14" spans="1:75">
@@ -3964,13 +3967,13 @@
         <v>108</v>
       </c>
       <c r="BU14" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="BV14" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="BW14" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="15" spans="1:75">
@@ -4191,13 +4194,13 @@
         <v>108</v>
       </c>
       <c r="BU15" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="BV15" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="BW15" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="16" spans="1:75">
@@ -4418,13 +4421,13 @@
         <v>108</v>
       </c>
       <c r="BU16" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="BV16" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="BW16" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="17" spans="1:75">
@@ -4645,13 +4648,13 @@
         <v>108</v>
       </c>
       <c r="BU17" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="BV17" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="BW17" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="18" spans="1:75">
@@ -4872,13 +4875,13 @@
         <v>108</v>
       </c>
       <c r="BU18" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="BV18" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BW18" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="19" spans="1:75">
@@ -5054,16 +5057,16 @@
         <v>108</v>
       </c>
       <c r="BF19" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BG19" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BH19" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BI19" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BJ19" t="s">
         <v>108</v>
@@ -5081,31 +5084,31 @@
         <v>108</v>
       </c>
       <c r="BO19" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BP19" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BQ19" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BR19" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BS19" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BT19" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BU19" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="BV19" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="BW19" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="20" spans="1:75">
@@ -5326,13 +5329,13 @@
         <v>108</v>
       </c>
       <c r="BU20" t="s">
+        <v>124</v>
+      </c>
+      <c r="BV20" t="s">
         <v>123</v>
       </c>
-      <c r="BV20" t="s">
-        <v>122</v>
-      </c>
       <c r="BW20" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="21" spans="1:75">
@@ -5553,13 +5556,13 @@
         <v>108</v>
       </c>
       <c r="BU21" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="BV21" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="BW21" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="22" spans="1:75">
@@ -5780,13 +5783,13 @@
         <v>108</v>
       </c>
       <c r="BU22" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="BV22" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="BW22" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="23" spans="1:75">
@@ -6007,13 +6010,13 @@
         <v>108</v>
       </c>
       <c r="BU23" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="BV23" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BW23" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="24" spans="1:75">
@@ -6234,13 +6237,13 @@
         <v>108</v>
       </c>
       <c r="BU24" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="BV24" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="BW24" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="25" spans="1:75">
@@ -6461,13 +6464,13 @@
         <v>108</v>
       </c>
       <c r="BU25" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="BV25" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="BW25" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="26" spans="1:75">
@@ -6505,7 +6508,7 @@
         <v>108</v>
       </c>
       <c r="L26" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="M26" t="s">
         <v>108</v>
@@ -6544,157 +6547,157 @@
         <v>108</v>
       </c>
       <c r="Y26" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="Z26" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="AA26" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="AB26" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="AC26" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="AD26" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="AE26" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="AF26" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="AG26" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="AH26" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="AI26" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="AJ26" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="AK26" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="AL26" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="AM26" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="AN26" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="AO26" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="AP26" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="AQ26" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="AR26" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="AS26" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="AT26" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="AU26" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="AV26" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="AW26" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="AX26" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="AY26" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="AZ26" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BA26" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BB26" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BC26" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BD26" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BE26" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BF26" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BG26" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BH26" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BI26" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BJ26" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BK26" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BL26" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BM26" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BN26" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BO26" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BP26" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BQ26" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BR26" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BS26" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BT26" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BU26" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="BV26" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="BW26" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="27" spans="1:75">
@@ -6915,13 +6918,13 @@
         <v>108</v>
       </c>
       <c r="BU27" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="BV27" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BW27" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="28" spans="1:75">
@@ -7142,13 +7145,13 @@
         <v>108</v>
       </c>
       <c r="BU28" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="BV28" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="BW28" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="29" spans="1:75">
@@ -7369,13 +7372,13 @@
         <v>108</v>
       </c>
       <c r="BU29" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="BV29" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="BW29" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="30" spans="1:75">
@@ -7596,13 +7599,13 @@
         <v>108</v>
       </c>
       <c r="BU30" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="BV30" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="BW30" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="31" spans="1:75">
@@ -7823,13 +7826,13 @@
         <v>108</v>
       </c>
       <c r="BU31" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="BV31" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="BW31" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="32" spans="1:75">
@@ -8050,13 +8053,13 @@
         <v>108</v>
       </c>
       <c r="BU32" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="BV32" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="BW32" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="33" spans="1:75">
@@ -8277,13 +8280,13 @@
         <v>108</v>
       </c>
       <c r="BU33" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="BV33" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="BW33" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="34" spans="1:75">
@@ -8504,13 +8507,13 @@
         <v>108</v>
       </c>
       <c r="BU34" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="BV34" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="BW34" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/ToT_(Labour/Cereal)_tukey_classification_matrix.xlsx
+++ b/outputs/ToT_(Labour/Cereal)_tukey_classification_matrix.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2550" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2550" uniqueCount="111">
   <si>
     <t>2020 May</t>
   </si>
@@ -343,79 +343,10 @@
     <t>Minimal</t>
   </si>
   <si>
-    <t>Alert</t>
-  </si>
-  <si>
-    <t>Alarm</t>
-  </si>
-  <si>
     <t>No data</t>
   </si>
   <si>
-    <t>23%</t>
-  </si>
-  <si>
-    <t>21%</t>
-  </si>
-  <si>
-    <t>10%</t>
-  </si>
-  <si>
-    <t>7%</t>
-  </si>
-  <si>
-    <t>27%</t>
-  </si>
-  <si>
-    <t>15%</t>
-  </si>
-  <si>
-    <t>20%</t>
-  </si>
-  <si>
-    <t>13%</t>
-  </si>
-  <si>
-    <t>17%</t>
-  </si>
-  <si>
-    <t>8%</t>
-  </si>
-  <si>
-    <t>18%</t>
-  </si>
-  <si>
-    <t>4%</t>
-  </si>
-  <si>
-    <t>11%</t>
-  </si>
-  <si>
     <t>0%</t>
-  </si>
-  <si>
-    <t>14%</t>
-  </si>
-  <si>
-    <t>25%</t>
-  </si>
-  <si>
-    <t>1%</t>
-  </si>
-  <si>
-    <t>3%</t>
-  </si>
-  <si>
-    <t>6%</t>
-  </si>
-  <si>
-    <t>24%</t>
-  </si>
-  <si>
-    <t>28%</t>
-  </si>
-  <si>
-    <t>30%</t>
   </si>
 </sst>
 </file>
@@ -1075,55 +1006,55 @@
         <v>108</v>
       </c>
       <c r="Q2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="S2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="T2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="U2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="X2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Y2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Z2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AA2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH2" t="s">
         <v>108</v>
@@ -1243,13 +1174,13 @@
         <v>108</v>
       </c>
       <c r="BU2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BV2" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="BW2" t="s">
-        <v>131</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3" spans="1:75">
@@ -1302,61 +1233,61 @@
         <v>108</v>
       </c>
       <c r="Q3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="S3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="T3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="U3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="X3" t="s">
         <v>108</v>
       </c>
       <c r="Y3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Z3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AA3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB3" t="s">
         <v>108</v>
       </c>
       <c r="AC3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AJ3" t="s">
         <v>108</v>
@@ -1470,13 +1401,13 @@
         <v>108</v>
       </c>
       <c r="BU3" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="BV3" t="s">
-        <v>129</v>
+        <v>110</v>
       </c>
       <c r="BW3" t="s">
-        <v>131</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:75">
@@ -1553,43 +1484,43 @@
         <v>108</v>
       </c>
       <c r="Y4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Z4" t="s">
         <v>108</v>
       </c>
       <c r="AA4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AJ4" t="s">
         <v>108</v>
       </c>
       <c r="AK4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AL4" t="s">
         <v>108</v>
@@ -1697,13 +1628,13 @@
         <v>108</v>
       </c>
       <c r="BU4" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="BV4" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="BW4" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
     </row>
     <row r="5" spans="1:75">
@@ -1762,7 +1693,7 @@
         <v>108</v>
       </c>
       <c r="S5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="T5" t="s">
         <v>108</v>
@@ -1780,28 +1711,28 @@
         <v>108</v>
       </c>
       <c r="Y5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Z5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AA5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AG5" t="s">
         <v>108</v>
@@ -1924,13 +1855,13 @@
         <v>108</v>
       </c>
       <c r="BU5" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="BV5" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="BW5" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
     </row>
     <row r="6" spans="1:75">
@@ -1986,64 +1917,64 @@
         <v>108</v>
       </c>
       <c r="R6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="S6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="T6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="U6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="X6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Y6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Z6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AA6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AJ6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AK6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AL6" t="s">
         <v>108</v>
@@ -2151,13 +2082,13 @@
         <v>108</v>
       </c>
       <c r="BU6" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="BV6" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="BW6" t="s">
-        <v>132</v>
+        <v>110</v>
       </c>
     </row>
     <row r="7" spans="1:75">
@@ -2237,37 +2168,37 @@
         <v>108</v>
       </c>
       <c r="Z7" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AA7" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB7" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC7" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD7" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE7" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF7" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG7" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH7" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI7" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AJ7" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AK7" t="s">
         <v>108</v>
@@ -2330,61 +2261,61 @@
         <v>108</v>
       </c>
       <c r="BE7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BF7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BG7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BH7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BI7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BJ7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BK7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BL7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BM7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BN7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BO7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BP7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BQ7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BR7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BS7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BT7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BU7" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="BV7" t="s">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="BW7" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
     </row>
     <row r="8" spans="1:75">
@@ -2431,7 +2362,7 @@
         <v>108</v>
       </c>
       <c r="O8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="P8" t="s">
         <v>108</v>
@@ -2443,49 +2374,49 @@
         <v>108</v>
       </c>
       <c r="S8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="T8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="U8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="X8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Y8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Z8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AA8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH8" t="s">
         <v>108</v>
@@ -2605,13 +2536,13 @@
         <v>108</v>
       </c>
       <c r="BU8" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="BV8" t="s">
-        <v>129</v>
+        <v>110</v>
       </c>
       <c r="BW8" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="9" spans="1:75">
@@ -2670,49 +2601,49 @@
         <v>108</v>
       </c>
       <c r="S9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="T9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="U9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="V9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="X9" t="s">
         <v>108</v>
       </c>
       <c r="Y9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Z9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AA9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH9" t="s">
         <v>108</v>
@@ -2832,13 +2763,13 @@
         <v>108</v>
       </c>
       <c r="BU9" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="BV9" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="BW9" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
     </row>
     <row r="10" spans="1:75">
@@ -2846,10 +2777,10 @@
         <v>83</v>
       </c>
       <c r="B10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D10" t="s">
         <v>108</v>
@@ -2897,13 +2828,13 @@
         <v>108</v>
       </c>
       <c r="S10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="T10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="U10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="V10" t="s">
         <v>108</v>
@@ -2915,22 +2846,22 @@
         <v>108</v>
       </c>
       <c r="Y10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Z10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AA10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE10" t="s">
         <v>108</v>
@@ -3059,13 +2990,13 @@
         <v>108</v>
       </c>
       <c r="BU10" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="BV10" t="s">
-        <v>129</v>
+        <v>110</v>
       </c>
       <c r="BW10" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
     </row>
     <row r="11" spans="1:75">
@@ -3124,22 +3055,22 @@
         <v>108</v>
       </c>
       <c r="S11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="T11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="U11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="X11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Y11" t="s">
         <v>108</v>
@@ -3151,16 +3082,16 @@
         <v>108</v>
       </c>
       <c r="AB11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF11" t="s">
         <v>108</v>
@@ -3175,7 +3106,7 @@
         <v>108</v>
       </c>
       <c r="AJ11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AK11" t="s">
         <v>108</v>
@@ -3286,13 +3217,13 @@
         <v>108</v>
       </c>
       <c r="BU11" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="BV11" t="s">
-        <v>129</v>
+        <v>110</v>
       </c>
       <c r="BW11" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
     </row>
     <row r="12" spans="1:75">
@@ -3342,7 +3273,7 @@
         <v>108</v>
       </c>
       <c r="P12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Q12" t="s">
         <v>108</v>
@@ -3351,61 +3282,61 @@
         <v>108</v>
       </c>
       <c r="S12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="T12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="U12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="X12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Y12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Z12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AA12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AJ12" t="s">
         <v>108</v>
       </c>
       <c r="AK12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AL12" t="s">
         <v>108</v>
@@ -3513,13 +3444,13 @@
         <v>108</v>
       </c>
       <c r="BU12" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="BV12" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="BW12" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
     </row>
     <row r="13" spans="1:75">
@@ -3578,46 +3509,46 @@
         <v>108</v>
       </c>
       <c r="S13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="T13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="U13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="X13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Y13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Z13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AA13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE13" t="s">
         <v>108</v>
       </c>
       <c r="AF13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG13" t="s">
         <v>108</v>
@@ -3740,13 +3671,13 @@
         <v>108</v>
       </c>
       <c r="BU13" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="BV13" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="BW13" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
     </row>
     <row r="14" spans="1:75">
@@ -3811,7 +3742,7 @@
         <v>108</v>
       </c>
       <c r="U14" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="V14" t="s">
         <v>108</v>
@@ -3823,31 +3754,31 @@
         <v>108</v>
       </c>
       <c r="Y14" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Z14" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AA14" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB14" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC14" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD14" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE14" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AF14" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AG14" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH14" t="s">
         <v>108</v>
@@ -3889,7 +3820,7 @@
         <v>108</v>
       </c>
       <c r="AU14" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AV14" t="s">
         <v>108</v>
@@ -3967,13 +3898,13 @@
         <v>108</v>
       </c>
       <c r="BU14" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="BV14" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="BW14" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
     </row>
     <row r="15" spans="1:75">
@@ -4041,7 +3972,7 @@
         <v>108</v>
       </c>
       <c r="V15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="W15" t="s">
         <v>108</v>
@@ -4056,31 +3987,31 @@
         <v>108</v>
       </c>
       <c r="AA15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AE15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AF15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH15" t="s">
         <v>108</v>
       </c>
       <c r="AI15" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AJ15" t="s">
         <v>108</v>
@@ -4194,13 +4125,13 @@
         <v>108</v>
       </c>
       <c r="BU15" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="BV15" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="BW15" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
     </row>
     <row r="16" spans="1:75">
@@ -4265,10 +4196,10 @@
         <v>108</v>
       </c>
       <c r="U16" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="V16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W16" t="s">
         <v>108</v>
@@ -4280,31 +4211,31 @@
         <v>108</v>
       </c>
       <c r="Z16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AA16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH16" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI16" t="s">
         <v>108</v>
@@ -4421,13 +4352,13 @@
         <v>108</v>
       </c>
       <c r="BU16" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="BV16" t="s">
-        <v>129</v>
+        <v>110</v>
       </c>
       <c r="BW16" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
     </row>
     <row r="17" spans="1:75">
@@ -4495,46 +4426,46 @@
         <v>108</v>
       </c>
       <c r="V17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="W17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="X17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Y17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Z17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AA17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH17" t="s">
         <v>108</v>
       </c>
       <c r="AI17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AJ17" t="s">
         <v>108</v>
@@ -4648,13 +4579,13 @@
         <v>108</v>
       </c>
       <c r="BU17" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="BV17" t="s">
-        <v>129</v>
+        <v>110</v>
       </c>
       <c r="BW17" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
     </row>
     <row r="18" spans="1:75">
@@ -4731,46 +4662,46 @@
         <v>108</v>
       </c>
       <c r="Y18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Z18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AA18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AJ18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AK18" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AL18" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AM18" t="s">
         <v>108</v>
@@ -4875,13 +4806,13 @@
         <v>108</v>
       </c>
       <c r="BU18" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="BV18" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="BW18" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
     </row>
     <row r="19" spans="1:75">
@@ -4946,128 +4877,128 @@
         <v>108</v>
       </c>
       <c r="U19" t="s">
+        <v>108</v>
+      </c>
+      <c r="V19" t="s">
+        <v>108</v>
+      </c>
+      <c r="W19" t="s">
+        <v>108</v>
+      </c>
+      <c r="X19" t="s">
+        <v>108</v>
+      </c>
+      <c r="Y19" t="s">
+        <v>108</v>
+      </c>
+      <c r="Z19" t="s">
+        <v>108</v>
+      </c>
+      <c r="AA19" t="s">
+        <v>108</v>
+      </c>
+      <c r="AB19" t="s">
+        <v>108</v>
+      </c>
+      <c r="AC19" t="s">
+        <v>108</v>
+      </c>
+      <c r="AD19" t="s">
+        <v>108</v>
+      </c>
+      <c r="AE19" t="s">
+        <v>108</v>
+      </c>
+      <c r="AF19" t="s">
+        <v>108</v>
+      </c>
+      <c r="AG19" t="s">
+        <v>108</v>
+      </c>
+      <c r="AH19" t="s">
+        <v>108</v>
+      </c>
+      <c r="AI19" t="s">
+        <v>108</v>
+      </c>
+      <c r="AJ19" t="s">
+        <v>108</v>
+      </c>
+      <c r="AK19" t="s">
+        <v>108</v>
+      </c>
+      <c r="AL19" t="s">
+        <v>108</v>
+      </c>
+      <c r="AM19" t="s">
+        <v>108</v>
+      </c>
+      <c r="AN19" t="s">
+        <v>108</v>
+      </c>
+      <c r="AO19" t="s">
+        <v>108</v>
+      </c>
+      <c r="AP19" t="s">
+        <v>108</v>
+      </c>
+      <c r="AQ19" t="s">
+        <v>108</v>
+      </c>
+      <c r="AR19" t="s">
+        <v>108</v>
+      </c>
+      <c r="AS19" t="s">
+        <v>108</v>
+      </c>
+      <c r="AT19" t="s">
+        <v>108</v>
+      </c>
+      <c r="AU19" t="s">
+        <v>108</v>
+      </c>
+      <c r="AV19" t="s">
+        <v>108</v>
+      </c>
+      <c r="AW19" t="s">
+        <v>108</v>
+      </c>
+      <c r="AX19" t="s">
+        <v>108</v>
+      </c>
+      <c r="AY19" t="s">
+        <v>108</v>
+      </c>
+      <c r="AZ19" t="s">
+        <v>108</v>
+      </c>
+      <c r="BA19" t="s">
+        <v>108</v>
+      </c>
+      <c r="BB19" t="s">
+        <v>108</v>
+      </c>
+      <c r="BC19" t="s">
+        <v>108</v>
+      </c>
+      <c r="BD19" t="s">
+        <v>108</v>
+      </c>
+      <c r="BE19" t="s">
+        <v>108</v>
+      </c>
+      <c r="BF19" t="s">
         <v>109</v>
       </c>
-      <c r="V19" t="s">
-        <v>108</v>
-      </c>
-      <c r="W19" t="s">
-        <v>108</v>
-      </c>
-      <c r="X19" t="s">
-        <v>108</v>
-      </c>
-      <c r="Y19" t="s">
-        <v>108</v>
-      </c>
-      <c r="Z19" t="s">
+      <c r="BG19" t="s">
         <v>109</v>
       </c>
-      <c r="AA19" t="s">
-        <v>108</v>
-      </c>
-      <c r="AB19" t="s">
-        <v>108</v>
-      </c>
-      <c r="AC19" t="s">
-        <v>108</v>
-      </c>
-      <c r="AD19" t="s">
-        <v>108</v>
-      </c>
-      <c r="AE19" t="s">
-        <v>108</v>
-      </c>
-      <c r="AF19" t="s">
-        <v>108</v>
-      </c>
-      <c r="AG19" t="s">
-        <v>110</v>
-      </c>
-      <c r="AH19" t="s">
-        <v>108</v>
-      </c>
-      <c r="AI19" t="s">
+      <c r="BH19" t="s">
         <v>109</v>
       </c>
-      <c r="AJ19" t="s">
-        <v>108</v>
-      </c>
-      <c r="AK19" t="s">
+      <c r="BI19" t="s">
         <v>109</v>
       </c>
-      <c r="AL19" t="s">
-        <v>110</v>
-      </c>
-      <c r="AM19" t="s">
-        <v>110</v>
-      </c>
-      <c r="AN19" t="s">
-        <v>108</v>
-      </c>
-      <c r="AO19" t="s">
-        <v>108</v>
-      </c>
-      <c r="AP19" t="s">
-        <v>108</v>
-      </c>
-      <c r="AQ19" t="s">
-        <v>108</v>
-      </c>
-      <c r="AR19" t="s">
-        <v>108</v>
-      </c>
-      <c r="AS19" t="s">
-        <v>108</v>
-      </c>
-      <c r="AT19" t="s">
-        <v>108</v>
-      </c>
-      <c r="AU19" t="s">
-        <v>108</v>
-      </c>
-      <c r="AV19" t="s">
-        <v>108</v>
-      </c>
-      <c r="AW19" t="s">
-        <v>108</v>
-      </c>
-      <c r="AX19" t="s">
-        <v>108</v>
-      </c>
-      <c r="AY19" t="s">
-        <v>108</v>
-      </c>
-      <c r="AZ19" t="s">
-        <v>108</v>
-      </c>
-      <c r="BA19" t="s">
-        <v>108</v>
-      </c>
-      <c r="BB19" t="s">
-        <v>108</v>
-      </c>
-      <c r="BC19" t="s">
-        <v>108</v>
-      </c>
-      <c r="BD19" t="s">
-        <v>108</v>
-      </c>
-      <c r="BE19" t="s">
-        <v>108</v>
-      </c>
-      <c r="BF19" t="s">
-        <v>111</v>
-      </c>
-      <c r="BG19" t="s">
-        <v>111</v>
-      </c>
-      <c r="BH19" t="s">
-        <v>111</v>
-      </c>
-      <c r="BI19" t="s">
-        <v>111</v>
-      </c>
       <c r="BJ19" t="s">
         <v>108</v>
       </c>
@@ -5084,31 +5015,31 @@
         <v>108</v>
       </c>
       <c r="BO19" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BP19" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BQ19" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BR19" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BS19" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BT19" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BU19" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="BV19" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="BW19" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="20" spans="1:75">
@@ -5185,37 +5116,37 @@
         <v>108</v>
       </c>
       <c r="Y20" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Z20" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AA20" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB20" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC20" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD20" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE20" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF20" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG20" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH20" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI20" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AJ20" t="s">
         <v>108</v>
@@ -5329,13 +5260,13 @@
         <v>108</v>
       </c>
       <c r="BU20" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="BV20" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="BW20" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
     </row>
     <row r="21" spans="1:75">
@@ -5364,10 +5295,10 @@
         <v>108</v>
       </c>
       <c r="I21" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J21" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K21" t="s">
         <v>108</v>
@@ -5394,37 +5325,37 @@
         <v>108</v>
       </c>
       <c r="S21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="T21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="U21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="X21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Y21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Z21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AA21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB21" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AC21" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AD21" t="s">
         <v>108</v>
@@ -5556,13 +5487,13 @@
         <v>108</v>
       </c>
       <c r="BU21" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="BV21" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="BW21" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
     </row>
     <row r="22" spans="1:75">
@@ -5627,49 +5558,49 @@
         <v>108</v>
       </c>
       <c r="U22" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="V22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W22" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="X22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Y22" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Z22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AA22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI22" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AJ22" t="s">
         <v>108</v>
@@ -5783,13 +5714,13 @@
         <v>108</v>
       </c>
       <c r="BU22" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="BV22" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="BW22" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="23" spans="1:75">
@@ -5866,28 +5797,28 @@
         <v>108</v>
       </c>
       <c r="Y23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Z23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AA23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD23" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE23" t="s">
         <v>108</v>
       </c>
       <c r="AF23" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AG23" t="s">
         <v>108</v>
@@ -6010,13 +5941,13 @@
         <v>108</v>
       </c>
       <c r="BU23" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="BV23" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="BW23" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="24" spans="1:75">
@@ -6075,40 +6006,40 @@
         <v>108</v>
       </c>
       <c r="S24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="T24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="U24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="X24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Y24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Z24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AA24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE24" t="s">
         <v>108</v>
@@ -6117,16 +6048,16 @@
         <v>108</v>
       </c>
       <c r="AG24" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH24" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI24" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AJ24" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AK24" t="s">
         <v>108</v>
@@ -6237,13 +6168,13 @@
         <v>108</v>
       </c>
       <c r="BU24" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="BV24" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="BW24" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="25" spans="1:75">
@@ -6302,58 +6233,58 @@
         <v>108</v>
       </c>
       <c r="S25" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="T25" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="U25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="X25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Y25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Z25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AA25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AJ25" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AK25" t="s">
         <v>108</v>
@@ -6464,13 +6395,13 @@
         <v>108</v>
       </c>
       <c r="BU25" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="BV25" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="BW25" t="s">
-        <v>127</v>
+        <v>110</v>
       </c>
     </row>
     <row r="26" spans="1:75">
@@ -6508,10 +6439,10 @@
         <v>108</v>
       </c>
       <c r="L26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="M26" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="N26" t="s">
         <v>108</v>
@@ -6544,160 +6475,160 @@
         <v>108</v>
       </c>
       <c r="X26" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Y26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="Z26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AA26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AB26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AC26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AD26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AE26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AF26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AG26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AH26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AI26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AJ26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AK26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AL26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AM26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AN26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AO26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AP26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AQ26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AR26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AS26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AT26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AU26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AV26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AW26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AX26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AY26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AZ26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BA26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BB26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BC26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BD26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BE26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BF26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BG26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BH26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BI26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BJ26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BK26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BL26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BM26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BN26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BO26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BP26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BQ26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BR26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BS26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BT26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BU26" t="s">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="BV26" t="s">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="BW26" t="s">
-        <v>125</v>
+        <v>110</v>
       </c>
     </row>
     <row r="27" spans="1:75">
@@ -6705,13 +6636,13 @@
         <v>100</v>
       </c>
       <c r="B27" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E27" t="s">
         <v>108</v>
@@ -6765,7 +6696,7 @@
         <v>108</v>
       </c>
       <c r="V27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W27" t="s">
         <v>108</v>
@@ -6774,22 +6705,22 @@
         <v>108</v>
       </c>
       <c r="Y27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Z27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AA27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE27" t="s">
         <v>108</v>
@@ -6810,7 +6741,7 @@
         <v>108</v>
       </c>
       <c r="AK27" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AL27" t="s">
         <v>108</v>
@@ -6918,13 +6849,13 @@
         <v>108</v>
       </c>
       <c r="BU27" t="s">
-        <v>126</v>
+        <v>110</v>
       </c>
       <c r="BV27" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="BW27" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
     </row>
     <row r="28" spans="1:75">
@@ -6989,46 +6920,46 @@
         <v>108</v>
       </c>
       <c r="U28" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="V28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="X28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Y28" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Z28" t="s">
         <v>108</v>
       </c>
       <c r="AA28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC28" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD28" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AE28" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AF28" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AG28" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH28" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI28" t="s">
         <v>108</v>
@@ -7145,13 +7076,13 @@
         <v>108</v>
       </c>
       <c r="BU28" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="BV28" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="BW28" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
     </row>
     <row r="29" spans="1:75">
@@ -7216,13 +7147,13 @@
         <v>108</v>
       </c>
       <c r="U29" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="V29" t="s">
         <v>108</v>
       </c>
       <c r="W29" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="X29" t="s">
         <v>108</v>
@@ -7234,19 +7165,19 @@
         <v>108</v>
       </c>
       <c r="AA29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE29" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AF29" t="s">
         <v>108</v>
@@ -7255,10 +7186,10 @@
         <v>108</v>
       </c>
       <c r="AH29" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AI29" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AJ29" t="s">
         <v>108</v>
@@ -7372,13 +7303,13 @@
         <v>108</v>
       </c>
       <c r="BU29" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="BV29" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="BW29" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
     </row>
     <row r="30" spans="1:75">
@@ -7446,34 +7377,34 @@
         <v>108</v>
       </c>
       <c r="V30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="X30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Y30" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Z30" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AA30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE30" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AF30" t="s">
         <v>108</v>
@@ -7482,13 +7413,13 @@
         <v>108</v>
       </c>
       <c r="AH30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AJ30" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AK30" t="s">
         <v>108</v>
@@ -7599,13 +7530,13 @@
         <v>108</v>
       </c>
       <c r="BU30" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="BV30" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="BW30" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
     </row>
     <row r="31" spans="1:75">
@@ -7676,31 +7607,31 @@
         <v>108</v>
       </c>
       <c r="W31" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="X31" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Y31" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Z31" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AA31" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB31" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC31" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD31" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE31" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF31" t="s">
         <v>108</v>
@@ -7712,13 +7643,13 @@
         <v>108</v>
       </c>
       <c r="AI31" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AJ31" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AK31" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AL31" t="s">
         <v>108</v>
@@ -7826,13 +7757,13 @@
         <v>108</v>
       </c>
       <c r="BU31" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="BV31" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="BW31" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
     </row>
     <row r="32" spans="1:75">
@@ -7855,7 +7786,7 @@
         <v>108</v>
       </c>
       <c r="G32" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H32" t="s">
         <v>108</v>
@@ -7882,64 +7813,64 @@
         <v>108</v>
       </c>
       <c r="P32" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="R32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="S32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="T32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="U32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="X32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Y32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="Z32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AA32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG32" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AH32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AJ32" t="s">
         <v>108</v>
@@ -8053,13 +7984,13 @@
         <v>108</v>
       </c>
       <c r="BU32" t="s">
-        <v>127</v>
+        <v>110</v>
       </c>
       <c r="BV32" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="BW32" t="s">
-        <v>133</v>
+        <v>110</v>
       </c>
     </row>
     <row r="33" spans="1:75">
@@ -8142,52 +8073,52 @@
         <v>108</v>
       </c>
       <c r="AA33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB33" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AC33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AJ33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AK33" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AL33" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AM33" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AN33" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AO33" t="s">
         <v>108</v>
       </c>
       <c r="AP33" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AQ33" t="s">
         <v>108</v>
@@ -8280,13 +8211,13 @@
         <v>108</v>
       </c>
       <c r="BU33" t="s">
-        <v>126</v>
+        <v>110</v>
       </c>
       <c r="BV33" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="BW33" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="34" spans="1:75">
@@ -8318,13 +8249,13 @@
         <v>108</v>
       </c>
       <c r="J34" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K34" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L34" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="M34" t="s">
         <v>108</v>
@@ -8351,13 +8282,13 @@
         <v>108</v>
       </c>
       <c r="U34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="W34" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="X34" t="s">
         <v>108</v>
@@ -8369,34 +8300,34 @@
         <v>108</v>
       </c>
       <c r="AA34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AB34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AC34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AD34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AE34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AF34" t="s">
         <v>108</v>
       </c>
       <c r="AG34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AJ34" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AK34" t="s">
         <v>108</v>
@@ -8507,13 +8438,13 @@
         <v>108</v>
       </c>
       <c r="BU34" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="BV34" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="BW34" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/ToT_(Labour/Cereal)_tukey_classification_matrix.xlsx
+++ b/outputs/ToT_(Labour/Cereal)_tukey_classification_matrix.xlsx
@@ -340,7 +340,7 @@
     <t>Zabul</t>
   </si>
   <si>
-    <t>Minimal</t>
+    <t>No concern</t>
   </si>
   <si>
     <t>No data</t>
